--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -690,103 +690,101 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">227
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -810,8 +808,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -843,18 +840,18 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2608
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -884,7 +881,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -896,7 +893,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -914,7 +911,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
@@ -926,7 +923,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -938,13 +935,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -974,8 +971,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1043,7 +1039,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1067,7 +1063,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">9885
 </t>
         </is>
       </c>
@@ -1091,7 +1087,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -1133,7 +1129,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1172,127 +1168,126 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">2729
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1325,132 +1320,131 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">543
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1094
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t xml:space="preserve">8706
+</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">3578
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">3080
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">1352
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">3891
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1483,125 +1477,131 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9274
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">2 066
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
-</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308 10
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">240
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2729
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1634,130 +1634,131 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">771
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">5635
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1778,90 +1779,89 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203
+          <t xml:space="preserve">4263
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29332
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1873,48 +1873,49 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1941,137 +1942,136 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9233
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2728
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -2092,145 +2092,145 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">23621
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">2921
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">12925
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">2723
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2251,145 +2251,145 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">253
+1
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">028
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0606
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">3600
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2422,133 +2422,133 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">7337
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">763
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1365
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">758
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">3861
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">424
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2568,138 +2568,143 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t xml:space="preserve">15308
+</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
-</t>
+          <t>0545</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0289
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">019
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
+          <t xml:space="preserve">36065
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">280
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
+          <t xml:space="preserve">7256
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2720,8 +2725,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
-</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2732,128 +2736,127 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>519</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">1394
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">067
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">668
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2874,89 +2877,89 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3365
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -2968,48 +2971,48 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3030,145 +3033,145 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">263
 </t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">605
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1257
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3188,67 +3191,65 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3260,25 +3261,25 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">10068
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3290,43 +3291,42 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">2424
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t xml:space="preserve">354
+</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3346,66 +3346,66 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">2949
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">61 1
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3423,66 +3423,68 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t xml:space="preserve">240
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3502,145 +3504,140 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">1554
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>53155</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>651</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4940
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">13
 </t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">000
-</t>
-        </is>
-      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">3200
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">783
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4420
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3661,142 +3658,143 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150519
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">3 2
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>651</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9728
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19116
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18993
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t xml:space="preserve">281
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3817,79 +3815,84 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">74
+15156
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3898,52 +3901,55 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">4
 </t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3964,47 +3970,54 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4015,13 +4028,13 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
@@ -4031,17 +4044,22 @@
 </t>
         </is>
       </c>
-      <c r="P25" s="3" t="n">
-        <v/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v/>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
@@ -4051,17 +4069,18 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>236</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4079,14 +4098,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">9526
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4112,37 +4130,37 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">16861
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4154,19 +4172,19 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4184,7 +4202,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4196,7 +4214,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -4214,13 +4232,13 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4232,19 +4250,19 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4264,13 +4282,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>329</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4281,37 +4299,37 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4323,7 +4341,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4335,13 +4353,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
@@ -4383,8 +4400,7 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>655</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
@@ -4395,14 +4411,12 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4428,8 +4442,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4440,25 +4453,24 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4470,19 +4482,18 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12201
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
@@ -4494,19 +4505,19 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -4530,7 +4541,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -4554,13 +4565,12 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4587,14 +4597,13 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1585
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4605,19 +4614,18 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
@@ -4629,7 +4637,8 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>684</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4658,7 +4667,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4682,7 +4691,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -4712,12 +4721,12 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -4744,76 +4753,79 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15065
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t xml:space="preserve">9961
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">1728
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
+          <t xml:space="preserve">4295
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4825,12 +4837,14 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4847,29 +4861,32 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">153
+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">26
+4
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -4896,37 +4913,37 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">2906
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4936,18 +4953,19 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -4959,7 +4977,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">9789
 </t>
         </is>
       </c>
@@ -4971,25 +4989,25 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">2391
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">2424
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">6 89
 </t>
         </is>
       </c>
@@ -5007,26 +5025,27 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">1141
+22
+171971191 7
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5052,83 +5071,86 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">290
 </t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1247
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -5137,13 +5159,14 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5154,7 +5177,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">2831
 </t>
         </is>
       </c>
@@ -5172,13 +5195,14 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">1717177
+23
+83
 </t>
         </is>
       </c>
@@ -5205,7 +5229,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
@@ -5217,43 +5241,43 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2249
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5271,13 +5295,13 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9808
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5295,7 +5319,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -5330,12 +5354,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>287</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5355,12 +5380,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
@@ -5372,44 +5397,47 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">2439
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">20612
 </t>
         </is>
       </c>
@@ -5421,19 +5449,19 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">9808
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2 20
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -5451,7 +5479,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -5463,7 +5491,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
@@ -5487,8 +5515,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5514,7 +5541,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5532,49 +5559,48 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">0 6
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">13 72
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5622,7 +5648,8 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>663</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -5645,7 +5672,8 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5671,7 +5699,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
@@ -5683,25 +5711,26 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">2439
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">222725
+1142811042
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">0 6
 </t>
         </is>
       </c>
@@ -5713,7 +5742,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">13 72
 </t>
         </is>
       </c>
@@ -5731,19 +5760,19 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
@@ -5773,13 +5802,12 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">2414
 </t>
         </is>
       </c>
@@ -5791,17 +5819,19 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -5822,24 +5852,25 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>00401</t>
+          <t xml:space="preserve">0600
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5856,39 +5887,44 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">58
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>12034446</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>0444</t>
+          <t xml:space="preserve">777
+22
+7
+</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">4250
 </t>
         </is>
       </c>
@@ -5900,19 +5936,19 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
+          <t xml:space="preserve">13341
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112879
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
@@ -5936,15 +5972,12 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v/>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
@@ -5954,7 +5987,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -5987,8 +6020,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5999,7 +6031,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -6011,7 +6043,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6032,8 +6064,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -6050,12 +6081,15 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
@@ -6065,13 +6099,13 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -6089,18 +6123,19 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">83248
 </t>
         </is>
       </c>
@@ -6127,20 +6162,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6157,19 +6191,19 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
@@ -6177,18 +6211,22 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">7 29
+15
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
@@ -6198,66 +6236,63 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">061
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6277,143 +6312,141 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v/>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>988</t>
+          <t xml:space="preserve">9906
+</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
+          <t xml:space="preserve">654
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6434,144 +6467,142 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">442
+111
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -6592,140 +6623,143 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">369
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2528
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106182
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6745,12 +6779,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
+          <t xml:space="preserve">3116
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6768,28 +6803,31 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0196
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6808,12 +6846,15 @@
 </t>
         </is>
       </c>
-      <c r="O43" s="3" t="n">
-        <v/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -6823,21 +6864,27 @@
 </t>
         </is>
       </c>
-      <c r="R43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6847,22 +6894,26 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6882,111 +6933,140 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
+          <t xml:space="preserve">3116
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7797
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254652
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4242
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42424
+211
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
         <v/>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+111562
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n">
         <v/>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1274
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>9346</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1038
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n">
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1463
+</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73733
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">781
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7260
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">797
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7518
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32423
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n">
         <v/>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4918
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124612
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -7005,36 +7085,38 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">14534
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t xml:space="preserve">305
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">7797
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">936
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -7043,71 +7125,71 @@
 </t>
         </is>
       </c>
-      <c r="J45" s="3" t="n">
-        <v/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
       </c>
       <c r="K45" s="3" t="n">
         <v/>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>4942</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="n">
         <v/>
       </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">984
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>645</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">717
 </t>
         </is>
       </c>
@@ -7125,13 +7207,13 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">32423
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">383
 </t>
         </is>
       </c>
@@ -7150,18 +7232,27 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2907
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">305
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -7173,13 +7264,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -7189,77 +7280,98 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2684
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2772
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1324
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="N46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v/>
-      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -685,12 +685,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -708,35 +708,37 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1210
+</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -748,49 +750,49 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">0975
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">1017
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">1330
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">112811
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">1561
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -802,18 +804,19 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t xml:space="preserve">1743
+</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -840,18 +843,18 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
@@ -881,73 +884,72 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -959,19 +961,20 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -991,7 +994,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">123680
 </t>
         </is>
       </c>
@@ -1009,13 +1012,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">12063
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">14103
 </t>
         </is>
       </c>
@@ -1027,73 +1030,69 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v/>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2213
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">2249
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1111,25 +1110,25 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1168,126 +1167,125 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>345</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">10113
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">19808
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">13119
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2729
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1308,7 +1306,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">193680
 </t>
         </is>
       </c>
@@ -1320,131 +1318,133 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t xml:space="preserve">1275
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">2417
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2333
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">282
 </t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8706
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3578
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3080
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">961
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1352
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
-</t>
-        </is>
-      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1465,143 +1465,109 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1617
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
+          <t xml:space="preserve">171836
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v/>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v/>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9274
+          <t xml:space="preserve">4870
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 066
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v/>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">13715
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">9080
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
+          <t xml:space="preserve">1901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v/>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2729
+          <t xml:space="preserve">10325
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">13891
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1622,7 +1588,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">23567
 </t>
         </is>
       </c>
@@ -1634,131 +1600,130 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
-</t>
-        </is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1974
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1311
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1275
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1616
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5635
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1779,89 +1744,90 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4263
-</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">3933
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">141
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -1873,49 +1839,49 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">1563
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">2295
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">26551
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1936,142 +1902,145 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">1418240
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2201
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">12203
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">19580
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2728
+          <t xml:space="preserve">1303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2092,145 +2061,142 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23621
+          <t xml:space="preserve">12301
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2921
+          <t xml:space="preserve">12291
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12925
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v/>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2723
+          <t xml:space="preserve">12291
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2251,145 +2217,144 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">18214
+</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">10195
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-1
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">028
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0606
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2416,138 +2381,138 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">10080
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7337
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">427
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">763
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1219
+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2566,38 +2531,33 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15308
-</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>0545</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">997
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
+          <t xml:space="preserve">1545
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
@@ -2609,102 +2569,79 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2066
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v/>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">14900
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36065
-</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
+          <t xml:space="preserve">1524
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v/>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">13310
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
+          <t xml:space="preserve">1763
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v/>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7256
+          <t xml:space="preserve">13861
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -2725,7 +2662,8 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t xml:space="preserve">3062
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2736,127 +2674,127 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">1980
+</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">067
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
+          <t xml:space="preserve">1273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v/>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">280
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">17172
+</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -2877,142 +2815,145 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3365
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>463</t>
+          <t xml:space="preserve">1257
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1672
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">10084
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2011
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">12298
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -3033,145 +2974,146 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">13262
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1243
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1317
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1253
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1885
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3191,95 +3133,93 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">12990
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1184
+</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">1198
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1197
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10068
-</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">22384
 </t>
         </is>
       </c>
@@ -3291,41 +3231,43 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">1716
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2424
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1263
+</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3346,144 +3288,141 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
+          <t xml:space="preserve">13575
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v/>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61 1
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">10010
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1631
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3504,140 +3443,141 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">12949
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
+          <t xml:space="preserve">15312
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>961</t>
+          <t xml:space="preserve">2188
+</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>53155</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v/>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>984</t>
+          <t xml:space="preserve">1691
+</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">783
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">12165
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3656,145 +3596,108 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v/>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v/>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
+          <t xml:space="preserve">1984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v/>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
+          <t xml:space="preserve">4940
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v/>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
+          <t xml:space="preserve">12529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v/>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">13200
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
+          <t xml:space="preserve">1796
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v/>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3815,141 +3718,137 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1092
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9881</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">103
 </t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>3516</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-15156
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">553
 </t>
         </is>
       </c>
@@ -3970,13 +3869,13 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -3988,36 +3887,34 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v/>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4028,31 +3925,31 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
-</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -4063,48 +3960,50 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">932
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1245
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9526
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4124,67 +4023,63 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16861
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v/>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -4196,7 +4091,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
@@ -4214,7 +4109,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
@@ -4232,37 +4127,37 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1743
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4282,54 +4177,50 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t xml:space="preserve">24182
+</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v/>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4347,18 +4238,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t xml:space="preserve">1990
+</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">042
 </t>
         </is>
       </c>
@@ -4370,19 +4262,19 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
@@ -4400,23 +4292,26 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t xml:space="preserve">2955
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">1302
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1742
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1105
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4442,35 +4337,36 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1326
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t xml:space="preserve">1184
+</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4482,7 +4378,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4493,31 +4389,30 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -4529,48 +4424,49 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">12603
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t xml:space="preserve">1860
+</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4591,53 +4487,55 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>803</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4649,37 +4547,36 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
@@ -4691,7 +4588,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -4703,30 +4600,31 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">1818
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4745,148 +4643,108 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13635
-</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9961
-</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v/>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">5069
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1721
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1728
-</t>
-        </is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v/>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295
+          <t xml:space="preserve">14895
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1455
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v/>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
+          <t xml:space="preserve">13445
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-4
-</t>
-        </is>
+          <t xml:space="preserve">1688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v/>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">14115
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -4913,37 +4771,37 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2906
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4953,99 +4811,95 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>616</t>
+          <t xml:space="preserve">1204
+</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9789
+          <t xml:space="preserve">1979
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2424
+          <t xml:space="preserve">2042
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 89
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">12067
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-22
-171971191 7
-</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5065,13 +4919,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">12635
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5083,66 +4937,64 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v/>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5153,19 +5005,19 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
@@ -5177,32 +5029,31 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2831
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1811
+</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1717177
-23
-83
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5223,13 +5074,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5241,43 +5092,40 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v/>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5289,21 +5137,18 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v/>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
@@ -5319,47 +5164,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">1252
+</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t xml:space="preserve">1918
+</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5380,12 +5227,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">11178
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2925
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
@@ -5397,47 +5245,46 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2439
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">11678
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v/>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20612
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -5449,25 +5296,25 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -5479,7 +5326,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
@@ -5491,31 +5338,32 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">1625
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5535,13 +5383,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
@@ -5553,66 +5401,62 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 6
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 72
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v/>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5624,19 +5468,19 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">2754
 </t>
         </is>
       </c>
@@ -5660,7 +5504,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -5672,7 +5516,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5693,13 +5537,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5711,38 +5555,37 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2439
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222725
-1142811042
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 6
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 72
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5760,34 +5603,34 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
@@ -5796,42 +5639,43 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">948
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2414
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5852,30 +5696,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0600
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
+          <t xml:space="preserve">8264
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v/>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
@@ -5887,46 +5723,33 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v/>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>10344</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-22
-7
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4250
-</t>
-        </is>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v/>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -5936,21 +5759,15 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13341
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">863
-</t>
-        </is>
+          <t xml:space="preserve">1331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v/>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
@@ -5960,34 +5777,28 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v/>
       </c>
       <c r="X37" s="3" t="n">
         <v/>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
+          <t xml:space="preserve">14160
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -6008,7 +5819,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">1633
 </t>
         </is>
       </c>
@@ -6020,7 +5831,8 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6031,27 +5843,24 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1686
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v/>
       </c>
       <c r="K38" s="3" t="n">
         <v/>
@@ -6064,7 +5873,8 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -6075,19 +5885,19 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
@@ -6099,43 +5909,43 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">19273
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">28111
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83248
+          <t xml:space="preserve">18392
 </t>
         </is>
       </c>
@@ -6162,19 +5972,20 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">1907
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">1693
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6191,58 +6002,62 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">935
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 29
-15
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">11307
+</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -6253,45 +6068,49 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>893</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t xml:space="preserve">1665
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t xml:space="preserve">1278
+</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>831</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">061
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
@@ -6312,94 +6131,96 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">12297
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">102
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9906
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
@@ -6411,7 +6232,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
@@ -6423,7 +6244,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -6435,13 +6256,14 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">722
+</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -6473,12 +6295,14 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t xml:space="preserve">296
+</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t xml:space="preserve">1208
+</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6489,7 +6313,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6501,108 +6325,108 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">15
 </t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-111
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">2093
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">18411
+</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6629,13 +6453,14 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6652,91 +6477,92 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106182
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12071
+</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -6747,18 +6573,19 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">12393
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1818
+</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6779,13 +6606,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">23116
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
@@ -6809,25 +6636,22 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v/>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -6837,48 +6661,51 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="n">
-        <v/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6890,30 +6717,31 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">1843
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6931,139 +6759,74 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3116
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7797
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254652
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4242
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42424
-211
-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v/>
       </c>
       <c r="J44" s="3" t="n">
         <v/>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-111562
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
+      <c r="K44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v/>
       </c>
       <c r="O44" s="3" t="n">
         <v/>
       </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1463
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73733
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7260
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">797
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7518
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32423
-</t>
-        </is>
+      <c r="P44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v/>
       </c>
       <c r="Z44" s="3" t="n">
         <v/>
@@ -7085,96 +6848,80 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14534
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7797
-</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1274
-</t>
-        </is>
+          <t xml:space="preserve">17227
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v/>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
+          <t xml:space="preserve">2936
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t xml:space="preserve">1649
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v/>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4942</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v/>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
@@ -7184,36 +6931,28 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
+          <t xml:space="preserve">16680
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v/>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32423
+          <t xml:space="preserve">9923
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
+          <t xml:space="preserve">1985
 </t>
         </is>
       </c>
@@ -7246,8 +6985,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -7258,118 +6996,117 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1887
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">187
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2684
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2772
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324
+          <t xml:space="preserve">12922
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -708,43 +708,43 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">2764
 </t>
         </is>
       </c>
@@ -756,7 +756,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -768,31 +768,31 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -804,21 +804,18 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
+          <t xml:space="preserve">17543
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v/>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -843,7 +840,8 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -854,7 +852,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -872,13 +870,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -890,36 +888,37 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">0 4
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -931,25 +930,25 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -967,7 +966,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -994,13 +993,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123680
+          <t xml:space="preserve">2681
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -1012,13 +1011,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12063
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1030,64 +1029,68 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">3124
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1098,7 +1101,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1110,25 +1113,25 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">454
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1167,7 +1170,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1179,24 +1182,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
@@ -1214,30 +1218,31 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13119
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -1249,13 +1254,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -1267,7 +1272,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1306,94 +1311,94 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193680
+          <t xml:space="preserve">96811
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">335
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">333
 </t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1275
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2417
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1965
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2333
-</t>
-        </is>
-      </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
@@ -1402,19 +1407,19 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -1465,34 +1470,49 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171836
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11850
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1617
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1074
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13549
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121008
+</t>
+        </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -1502,14 +1522,23 @@
 </t>
         </is>
       </c>
-      <c r="L9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1094
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11080
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1523,45 +1552,57 @@
 </t>
         </is>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1566
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13715
+          <t xml:space="preserve">1537905
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9080
+          <t xml:space="preserve">3080
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 2 20
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14200
+</t>
+        </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10325
+          <t xml:space="preserve">11395
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13891
+          <t xml:space="preserve">5891
 </t>
         </is>
       </c>
@@ -1588,13 +1629,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">8295
 </t>
         </is>
       </c>
@@ -1606,7 +1647,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -1618,15 +1659,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v/>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1634,8 +1672,11 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1657,7 +1698,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1669,19 +1710,19 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -1693,7 +1734,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -1705,7 +1746,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -1717,7 +1758,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">14178
 </t>
         </is>
       </c>
@@ -1744,36 +1785,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t xml:space="preserve">420
+</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3933
+          <t xml:space="preserve">9353
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -1785,19 +1827,19 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">10104
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
@@ -1815,13 +1857,13 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1839,7 +1881,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -1851,19 +1893,19 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26551
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -1875,7 +1917,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -1902,94 +1944,94 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418240
+          <t xml:space="preserve">12182
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">328
 </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2201
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12203
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2004,19 +2046,19 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19580
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -2034,13 +2076,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -2061,13 +2103,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12301
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2079,7 +2121,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2091,7 +2133,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2103,76 +2145,79 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -2190,13 +2235,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">8008
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -2217,7 +2262,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18214
+          <t xml:space="preserve">8214
 </t>
         </is>
       </c>
@@ -2229,7 +2274,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2241,36 +2286,37 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2282,31 +2328,31 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">0 4
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2324,7 +2370,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -2342,19 +2388,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2381,25 +2427,25 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -2411,18 +2457,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">4080
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2434,19 +2481,19 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -2458,7 +2505,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2470,7 +2517,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2482,38 +2529,37 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">7166
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2531,16 +2577,21 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153081
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15242
+</t>
+        </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2551,19 +2602,19 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545
+          <t xml:space="preserve">5245
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2575,28 +2626,37 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1624
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11290
+</t>
+        </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14900
+          <t xml:space="preserve">4900
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2606,42 +2666,57 @@
 </t>
         </is>
       </c>
-      <c r="R16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1257
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1427
+</t>
+        </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13310
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2512
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1400
+</t>
+        </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13861
+          <t xml:space="preserve">138611
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2680,13 +2755,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -2698,7 +2773,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2708,8 +2783,11 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2725,8 +2803,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2737,25 +2814,25 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">9305
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -2767,34 +2844,37 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17172
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2815,103 +2895,100 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11714
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">322
 </t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1257
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1672
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10084
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1894
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1322
-</t>
-        </is>
-      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2923,13 +3000,13 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2941,19 +3018,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2974,19 +3051,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13262
+          <t xml:space="preserve">3262
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -3004,7 +3081,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -3016,37 +3093,37 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -3064,25 +3141,25 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">2553
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3100,13 +3177,13 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -3133,18 +3210,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990
+          <t xml:space="preserve">28990
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3162,25 +3240,25 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3192,34 +3270,37 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22384
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3231,7 +3312,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
@@ -3255,13 +3336,13 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -3288,7 +3369,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13575
+          <t xml:space="preserve">3575
 </t>
         </is>
       </c>
@@ -3300,39 +3381,43 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18281
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3344,37 +3429,37 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10010
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">0 0
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3386,7 +3471,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -3404,7 +3489,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3416,13 +3501,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">184841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -3443,57 +3528,61 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12949
+          <t xml:space="preserve">9929
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15312
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3511,19 +3600,19 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">108000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3541,7 +3630,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
@@ -3553,19 +3642,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12165
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3596,28 +3685,39 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16101
+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1554
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3632,20 +3732,29 @@
 </t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
-        <v/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 78
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16133
+</t>
+        </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
@@ -3653,41 +3762,59 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="n">
-        <v/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12406
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153947
+</t>
+        </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13200
+          <t xml:space="preserve">3200
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">796 1
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406
+</t>
+        </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
@@ -3697,7 +3824,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3718,19 +3845,18 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">9311
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
@@ -3754,19 +3880,22 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
       </c>
       <c r="K24" s="3" t="n">
         <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3778,41 +3907,43 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
@@ -3830,26 +3961,25 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">553
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3869,7 +3999,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
@@ -3887,23 +4017,27 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -3913,7 +4047,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3925,24 +4059,25 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3960,7 +4095,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3972,37 +4107,37 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">9 52
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4023,24 +4158,25 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">9317
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -4052,12 +4188,15 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18868
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -4067,7 +4206,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4091,7 +4230,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4103,19 +4242,19 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3854
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4133,24 +4272,25 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -4177,7 +4317,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
+          <t xml:space="preserve">14182
 </t>
         </is>
       </c>
@@ -4189,38 +4329,43 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1387
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4238,19 +4383,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4262,19 +4407,19 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -4292,25 +4437,25 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2955
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1742
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -4343,7 +4488,8 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4360,13 +4506,13 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4378,7 +4524,8 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t xml:space="preserve">800
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4389,18 +4536,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4412,7 +4560,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">29798
 </t>
         </is>
       </c>
@@ -4424,37 +4572,37 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12603
+          <t xml:space="preserve">26595
 </t>
         </is>
       </c>
@@ -4466,8 +4614,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4487,7 +4634,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1221121
 </t>
         </is>
       </c>
@@ -4505,7 +4652,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">2472
 </t>
         </is>
       </c>
@@ -4523,7 +4670,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4533,11 +4680,8 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
+      <c r="K29" s="3" t="n">
+        <v/>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -4547,30 +4691,31 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">241 9
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4588,25 +4733,25 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4618,13 +4763,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4643,39 +4788,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6251
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">565
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11200
+</t>
+        </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -4685,60 +4842,87 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1802
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14895
+          <t xml:space="preserve">4895
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3121
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01 35
+</t>
+        </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13445
+          <t xml:space="preserve">3445
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14115
+          <t xml:space="preserve">4115
 </t>
         </is>
       </c>
@@ -4771,7 +4955,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">212461
 </t>
         </is>
       </c>
@@ -4783,25 +4967,25 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4816,89 +5000,91 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12067
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">1823
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16828
 </t>
         </is>
       </c>
@@ -4919,13 +5105,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12635
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4937,7 +5123,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4955,12 +5141,15 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -4976,19 +5165,20 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t xml:space="preserve">990
+</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5005,19 +5195,19 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
@@ -5029,31 +5219,31 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -5074,7 +5264,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -5098,13 +5288,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5114,12 +5304,14 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -5137,7 +5329,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -5147,8 +5339,11 @@
 </t>
         </is>
       </c>
-      <c r="P33" s="3" t="n">
-        <v/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
@@ -5164,49 +5359,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -5227,7 +5422,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11178
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5239,13 +5434,13 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24 9
 </t>
         </is>
       </c>
@@ -5257,7 +5452,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11678
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -5296,25 +5491,25 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -5326,25 +5521,25 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5356,13 +5551,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5383,25 +5578,25 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">2844
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -5419,12 +5614,13 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5436,21 +5632,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">2189
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -5468,19 +5668,19 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2754
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
@@ -5504,7 +5704,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">129593
 </t>
         </is>
       </c>
@@ -5516,7 +5716,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
@@ -5561,13 +5761,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5585,7 +5785,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -5603,19 +5803,19 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -5639,31 +5839,31 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5675,7 +5875,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -5700,18 +5900,27 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1429
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11215
+</t>
+        </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
@@ -5723,12 +5932,15 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -5742,32 +5954,47 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
@@ -5777,22 +6004,31 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1298
+</t>
+        </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14160
+          <t xml:space="preserve">124660
 </t>
         </is>
       </c>
@@ -5819,7 +6055,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1633
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -5831,7 +6067,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2 0 0
 </t>
         </is>
       </c>
@@ -5849,21 +6085,27 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1686
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 1
+</t>
+        </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -5873,7 +6115,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5885,7 +6127,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5897,7 +6139,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -5909,31 +6151,31 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">8287
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28111
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -5945,7 +6187,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18392
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
@@ -5972,19 +6214,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3320
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1693
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -6002,7 +6244,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -6014,13 +6256,13 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6044,19 +6286,19 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11307
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6074,7 +6316,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">66853
 </t>
         </is>
       </c>
@@ -6086,7 +6328,7 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">2 78
 </t>
         </is>
       </c>
@@ -6098,7 +6340,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2178
 </t>
         </is>
       </c>
@@ -6110,7 +6352,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -6131,7 +6373,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">2788
 </t>
         </is>
       </c>
@@ -6149,19 +6391,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12297
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -6173,13 +6415,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6191,12 +6433,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6208,19 +6451,19 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6232,19 +6475,19 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
+          <t xml:space="preserve">654
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6256,7 +6499,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -6268,7 +6511,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">18114
 </t>
         </is>
       </c>
@@ -6289,7 +6532,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">2486
 </t>
         </is>
       </c>
@@ -6301,7 +6544,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6313,7 +6556,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6325,7 +6568,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -6337,19 +6580,19 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6361,7 +6604,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -6373,7 +6616,7 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -6385,50 +6628,48 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18411
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
+          <t xml:space="preserve">1811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v/>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -6477,25 +6718,25 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6507,7 +6748,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6519,49 +6760,49 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12071
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -6573,7 +6814,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12393
+          <t xml:space="preserve">189535
 </t>
         </is>
       </c>
@@ -6606,7 +6847,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23116
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
@@ -6618,7 +6859,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -6640,8 +6881,11 @@
 </t>
         </is>
       </c>
-      <c r="I43" s="3" t="n">
-        <v/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1416
+</t>
+        </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -6663,49 +6907,49 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -6717,7 +6961,7 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -6729,18 +6973,18 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1843
+          <t xml:space="preserve">18495
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6759,8 +7003,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="n">
         <v/>
@@ -6848,33 +7095,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17227
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14234
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9227
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101011
+</t>
+        </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">121010
+</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2936
+          <t xml:space="preserve">936
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">025
 </t>
         </is>
       </c>
@@ -6886,42 +7142,54 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1009001604
+</t>
+        </is>
       </c>
       <c r="M45" s="3" t="n">
         <v/>
       </c>
-      <c r="N45" s="3" t="n">
-        <v/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161285
+</t>
+        </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">49160
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12463
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
@@ -6931,28 +7199,36 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16680
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">66 8
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2220
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14124
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923
-</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">108209
 </t>
         </is>
       </c>
@@ -6979,13 +7255,14 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6996,117 +7273,121 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2717
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2738
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1293
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>6451</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12922
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -744,7 +744,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2764
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -756,8 +756,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -774,7 +773,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -804,13 +803,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">2921
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17543
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -870,13 +869,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -894,7 +893,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -936,7 +935,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -960,7 +959,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -993,13 +992,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1011,13 +1010,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -1035,7 +1034,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1065,7 +1064,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
@@ -1077,7 +1076,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1101,7 +1100,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1125,13 +1124,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">454
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1152,7 +1151,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">82182
 </t>
         </is>
       </c>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1182,25 +1181,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -1260,7 +1259,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -1311,13 +1310,13 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96811
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -1335,7 +1334,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1347,7 +1346,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1359,7 +1358,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1383,7 +1382,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
@@ -1413,7 +1412,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -1449,7 +1448,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1470,7 +1469,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11850
+          <t xml:space="preserve">17830
 </t>
         </is>
       </c>
@@ -1488,7 +1487,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13549
+          <t xml:space="preserve">1345
 </t>
         </is>
       </c>
@@ -1500,7 +1499,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121008
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -1530,13 +1529,13 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11080
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">85566
 </t>
         </is>
       </c>
@@ -1566,7 +1565,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537905
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
@@ -1584,25 +1583,25 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2 20
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891
+          <t xml:space="preserve">3891
 </t>
         </is>
       </c>
@@ -1629,13 +1628,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">2567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1659,12 +1658,15 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1674,13 +1676,13 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1728,7 +1730,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">6 1 6
 </t>
         </is>
       </c>
@@ -1746,19 +1748,19 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14178
+          <t xml:space="preserve">8778
 </t>
         </is>
       </c>
@@ -1791,13 +1793,13 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9353
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
@@ -1809,37 +1811,37 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1887,7 +1889,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1563
+          <t xml:space="preserve">2563
 </t>
         </is>
       </c>
@@ -1923,7 +1925,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -1950,7 +1952,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1980,13 +1982,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2010,7 +2012,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2034,7 +2036,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -2046,7 +2048,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -2070,19 +2072,19 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2103,7 +2105,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">2381
 </t>
         </is>
       </c>
@@ -2139,7 +2141,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2181,7 +2183,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2229,13 +2231,13 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8008
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -2262,7 +2264,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8214
+          <t xml:space="preserve">12214
 </t>
         </is>
       </c>
@@ -2310,7 +2312,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2394,13 +2396,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -2433,52 +2435,52 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4080
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -2505,22 +2507,22 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">8300
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">300
 </t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">710
@@ -2529,13 +2531,13 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -2553,7 +2555,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7166
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -2585,7 +2587,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">1542
 </t>
         </is>
       </c>
@@ -2596,25 +2598,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2626,25 +2627,25 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -2668,13 +2669,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2686,19 +2687,19 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
@@ -2710,13 +2711,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138611
+          <t xml:space="preserve">3861
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -2743,8 +2744,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -2803,24 +2803,24 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -2838,13 +2838,13 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">19662
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -2862,13 +2862,13 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">7722
 </t>
         </is>
       </c>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2923,13 +2923,13 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11714
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2946,13 +2946,13 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -3030,8 +3030,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3081,7 +3080,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3117,7 +3116,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3135,13 +3134,13 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3159,19 +3158,19 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3210,7 +3209,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28990
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
@@ -3228,7 +3227,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -3240,7 +3239,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3324,13 +3323,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3381,7 +3380,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3393,25 +3392,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18281
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3441,13 +3440,13 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">8000
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 0
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3495,19 +3494,19 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184841
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3528,13 +3527,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9929
-</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -3552,13 +3550,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -3570,7 +3568,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3582,7 +3580,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
@@ -3600,19 +3598,19 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3636,7 +3634,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -3699,25 +3697,25 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">2258
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3734,7 +3732,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -3746,13 +3744,13 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 78
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3776,13 +3774,13 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12406
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153947
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
@@ -3794,26 +3792,25 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796 1
+          <t xml:space="preserve">795 1
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3824,7 +3821,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3845,12 +3842,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -3880,18 +3877,18 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3901,7 +3898,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3919,67 +3916,68 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">053
 </t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">640
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3999,7 +3997,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
@@ -4023,7 +4021,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4035,8 +4033,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4053,14 +4050,12 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>41104</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4119,7 +4114,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -4158,13 +4153,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8450
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -4188,13 +4183,13 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18868
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4206,7 +4201,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4224,8 +4219,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4234,15 +4228,12 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
+      <c r="P26" s="3" t="n">
+        <v/>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3854
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
@@ -4317,13 +4308,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -4341,7 +4332,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1387
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4353,7 +4344,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4383,7 +4374,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -4437,13 +4428,12 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">8082
 </t>
         </is>
       </c>
@@ -4482,7 +4472,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">3256
 </t>
         </is>
       </c>
@@ -4506,7 +4496,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4524,7 +4514,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4560,7 +4550,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29798
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -4584,7 +4574,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -4602,13 +4592,13 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26595
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4634,8 +4624,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221121
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4652,7 +4641,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4676,7 +4665,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4685,13 +4674,13 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2189
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241 9
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4721,7 +4710,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4739,7 +4728,7 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">1073
 </t>
         </is>
       </c>
@@ -4757,19 +4746,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4788,21 +4777,17 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6251
-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v/>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4814,49 +4799,48 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -4868,25 +4852,25 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01 35
+          <t xml:space="preserve">18 35
 </t>
         </is>
       </c>
@@ -4955,7 +4939,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212461
+          <t xml:space="preserve">513
 </t>
         </is>
       </c>
@@ -4967,19 +4951,16 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v/>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5006,7 +4987,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">20 2
 </t>
         </is>
       </c>
@@ -5054,19 +5035,19 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -5078,13 +5059,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16828
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5135,7 +5116,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -5147,7 +5128,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5231,19 +5212,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5264,7 +5245,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
@@ -5276,57 +5257,58 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2006
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
@@ -5365,7 +5347,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5401,7 +5383,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5434,7 +5416,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -5462,8 +5444,10 @@
 </t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
-        <v/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -5497,7 +5481,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5521,13 +5505,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5539,7 +5523,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5551,13 +5535,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5632,7 +5616,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5644,7 +5628,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">2149
 </t>
         </is>
       </c>
@@ -5680,7 +5664,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5704,7 +5688,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129593
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -5716,7 +5700,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5737,7 +5721,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5761,7 +5745,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5779,7 +5763,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5815,7 +5799,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -5843,11 +5827,8 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
+      <c r="U36" s="3" t="n">
+        <v/>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
@@ -5857,8 +5838,7 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5875,7 +5855,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5908,13 +5888,13 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -5938,103 +5918,103 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18079
+</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0229
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1338
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39236
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1034
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1363
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3936
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1298
-</t>
-        </is>
-      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124660
+          <t xml:space="preserve">4160
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6055,7 +6035,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
@@ -6085,7 +6065,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18 6
 </t>
         </is>
       </c>
@@ -6097,13 +6077,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">2 8
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6115,7 +6095,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6139,7 +6119,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2566
 </t>
         </is>
       </c>
@@ -6151,13 +6131,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
@@ -6169,7 +6148,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6181,13 +6160,13 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6214,7 +6193,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -6244,19 +6223,19 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6292,7 +6271,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
@@ -6316,7 +6295,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66853
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -6340,7 +6319,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -6373,13 +6352,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2788
+          <t xml:space="preserve">27281
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -6403,7 +6382,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6415,7 +6394,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6439,7 +6418,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6457,13 +6436,13 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6481,7 +6460,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -6511,7 +6490,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18114
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6532,7 +6511,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6580,7 +6559,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6616,13 +6595,13 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -6634,7 +6613,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6664,12 +6643,15 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -6718,7 +6700,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6730,7 +6712,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6748,7 +6730,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -6766,7 +6748,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -6814,13 +6796,13 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189535
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6847,26 +6829,25 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">3116
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6877,13 +6858,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6925,7 +6906,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6973,12 +6954,12 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>854</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18495
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
@@ -7101,24 +7082,25 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>705</t>
+          <t xml:space="preserve">1027
+</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101011
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121010
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
@@ -7130,25 +7112,25 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">025
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">18149
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009001604
+          <t xml:space="preserve">1050816
 </t>
         </is>
       </c>
@@ -7157,32 +7139,31 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161285
+          <t xml:space="preserve">18205
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49160
+          <t xml:space="preserve">4918
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">16 9
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12463
+          <t xml:space="preserve">8463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>633</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -7205,30 +7186,31 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14124
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t xml:space="preserve">99295
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108209
+          <t xml:space="preserve">0805
 </t>
         </is>
       </c>
@@ -7255,7 +7237,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -7273,13 +7255,13 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1091
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -7297,7 +7279,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7309,7 +7291,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -7333,7 +7315,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -7345,7 +7327,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2717
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -7357,37 +7339,37 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2738
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -685,7 +685,8 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>336</t>
+          <t xml:space="preserve">335
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -720,7 +721,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -744,7 +745,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -756,12 +757,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1330
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
@@ -773,7 +775,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -803,7 +805,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2921
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -813,8 +815,11 @@
 </t>
         </is>
       </c>
-      <c r="Z4" s="3" t="n">
-        <v/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -893,7 +898,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -911,7 +916,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -935,13 +940,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -965,13 +970,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -992,7 +997,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1016,7 +1021,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1034,7 +1039,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1064,13 +1069,13 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -1094,7 +1099,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">596
 </t>
         </is>
       </c>
@@ -1130,7 +1135,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1151,7 +1156,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -1181,7 +1186,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1193,13 +1198,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -1235,7 +1240,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1277,7 +1282,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1322,7 +1327,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
@@ -1346,7 +1351,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1382,13 +1387,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -1406,19 +1411,19 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -1436,7 +1441,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1448,7 +1453,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17830
+          <t xml:space="preserve">17836
 </t>
         </is>
       </c>
@@ -1493,7 +1498,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">543
 </t>
         </is>
       </c>
@@ -1535,7 +1540,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">12 82
 </t>
         </is>
       </c>
@@ -1547,13 +1552,13 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85566
+          <t xml:space="preserve">2556
 </t>
         </is>
       </c>
@@ -1565,7 +1570,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -1583,7 +1588,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
@@ -1595,7 +1600,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
@@ -1628,19 +1633,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -1658,13 +1663,13 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1676,13 +1681,13 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1706,7 +1711,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1730,13 +1735,13 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 1 6
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1760,13 +1765,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8778
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1793,49 +1798,48 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1889,7 +1893,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
@@ -1919,13 +1923,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12182
+          <t xml:space="preserve">24182
 </t>
         </is>
       </c>
@@ -1976,19 +1980,19 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2012,7 +2016,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
@@ -2036,7 +2040,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 8
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2054,7 +2058,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
@@ -2072,13 +2076,13 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">1303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">1732
 </t>
         </is>
       </c>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
@@ -2141,7 +2145,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -2171,7 +2175,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2183,7 +2187,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2243,7 +2247,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2264,7 +2268,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12214
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -2276,7 +2280,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
@@ -2294,7 +2298,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -2330,7 +2334,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2342,7 +2346,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2396,13 +2400,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2423,7 +2427,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">23408
 </t>
         </is>
       </c>
@@ -2465,7 +2469,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2489,7 +2493,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -2507,7 +2511,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2537,13 +2541,13 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2419
 </t>
         </is>
       </c>
@@ -2561,7 +2565,8 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2581,7 +2586,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153081
+          <t xml:space="preserve">15308
 </t>
         </is>
       </c>
@@ -2593,12 +2598,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>992</t>
+          <t xml:space="preserve">997
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">2268
+</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2609,7 +2616,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
@@ -2633,19 +2640,19 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2669,13 +2676,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
@@ -2687,19 +2694,19 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">763
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1365
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -2717,7 +2724,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1423
 </t>
         </is>
       </c>
@@ -2738,13 +2745,14 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">2306
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2755,7 +2763,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -2785,7 +2793,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2815,7 +2823,8 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2838,7 +2847,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19662
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
@@ -2868,13 +2877,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7722
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2895,12 +2904,14 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2911,30 +2922,31 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2952,13 +2964,13 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2970,7 +2982,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3000,7 +3012,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
@@ -3030,7 +3042,8 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3050,13 +3063,13 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
@@ -3116,7 +3129,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
@@ -3176,7 +3189,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3215,7 +3228,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -3233,13 +3246,13 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
@@ -3263,19 +3276,19 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">11197
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -3368,7 +3381,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
@@ -3380,7 +3393,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3398,7 +3411,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -3428,19 +3441,19 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
@@ -3500,7 +3513,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">18441
 </t>
         </is>
       </c>
@@ -3527,7 +3540,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t xml:space="preserve">2949
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3538,13 +3552,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">12380
 </t>
         </is>
       </c>
@@ -3556,7 +3570,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
@@ -3580,7 +3594,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3592,7 +3606,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
@@ -3604,13 +3618,13 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3628,13 +3642,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -3646,7 +3660,7 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -3658,7 +3672,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -3685,7 +3699,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3697,13 +3711,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">0962
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -3715,7 +3729,8 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">882
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3750,7 +3765,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
@@ -3780,7 +3795,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3792,25 +3807,26 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">795 1
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t xml:space="preserve">1406
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3821,7 +3837,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3842,7 +3858,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t xml:space="preserve">3220
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3853,7 +3870,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3881,12 +3898,15 @@
 </t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
-        <v/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3898,7 +3918,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -3910,7 +3930,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -3940,7 +3960,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
@@ -3952,7 +3972,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4033,7 +4053,8 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4050,12 +4071,13 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4114,7 +4136,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4126,7 +4148,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 52
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
@@ -4195,7 +4217,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -4219,7 +4241,8 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4228,12 +4251,15 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="n">
-        <v/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -4245,7 +4271,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -4332,7 +4358,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4344,7 +4370,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -4374,7 +4400,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4428,12 +4454,13 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8082
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4466,13 +4493,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3256
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
@@ -4484,7 +4511,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">2682
 </t>
         </is>
       </c>
@@ -4496,7 +4523,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4520,7 +4547,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
@@ -4586,13 +4613,13 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
@@ -4604,7 +4631,8 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4624,7 +4652,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4669,12 +4697,15 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
-        <v/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4710,7 +4741,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
@@ -4728,7 +4759,7 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1073
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4758,7 +4789,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4777,12 +4808,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t xml:space="preserve">11565
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4793,30 +4828,31 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11200
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">2569
+</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">11718
 </t>
         </is>
       </c>
@@ -4828,19 +4864,19 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -4858,19 +4894,19 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4900,13 +4936,13 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">24115
 </t>
         </is>
       </c>
@@ -4939,7 +4975,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">513
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
@@ -4955,8 +4991,11 @@
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
-        <v/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -4972,12 +5011,15 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4987,7 +5029,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 2
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4999,7 +5041,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5035,19 +5077,19 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">11138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -5065,7 +5107,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5092,88 +5134,87 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1290
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">290
 </t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -5182,7 +5223,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
@@ -5206,25 +5247,25 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5245,7 +5286,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -5257,7 +5298,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -5281,19 +5322,19 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5311,7 +5352,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -5347,7 +5388,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5381,11 +5422,8 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
+      <c r="Z33" s="3" t="n">
+        <v/>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -5422,7 +5460,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 9
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -5446,7 +5484,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5457,19 +5495,19 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1201
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -5628,7 +5666,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
@@ -5640,7 +5678,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5688,13 +5726,13 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">2093
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
@@ -5721,13 +5759,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -5745,13 +5783,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">11190
 </t>
         </is>
       </c>
@@ -5769,7 +5807,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5787,7 +5825,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -5827,8 +5865,11 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="n">
-        <v/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
@@ -5838,7 +5879,8 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>618</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5849,13 +5891,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5888,19 +5930,19 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
@@ -5918,13 +5960,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18079
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5936,49 +5978,49 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1338
+          <t xml:space="preserve">1331
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1363
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39236
+          <t xml:space="preserve">3936
 </t>
         </is>
       </c>
@@ -5990,19 +6032,19 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
@@ -6035,7 +6077,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6047,13 +6089,13 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0 0
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6065,7 +6107,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 6
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6077,13 +6119,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 8
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6095,7 +6137,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6119,7 +6161,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6131,24 +6173,25 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -6166,13 +6209,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6193,7 +6236,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">3323
 </t>
         </is>
       </c>
@@ -6217,7 +6260,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -6229,52 +6272,52 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5 8
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">35
 </t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">002
-</t>
-        </is>
-      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">307
@@ -6295,19 +6338,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 78
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -6319,19 +6362,19 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6352,19 +6395,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27281
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">12006
 </t>
         </is>
       </c>
@@ -6412,13 +6455,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6454,7 +6497,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
@@ -6472,7 +6515,7 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -6490,7 +6533,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -6517,7 +6560,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
@@ -6547,15 +6590,12 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v/>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -6571,7 +6611,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6613,7 +6653,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
@@ -6625,7 +6665,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
@@ -6637,19 +6677,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">8411
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -6730,13 +6770,13 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
@@ -6748,7 +6788,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6790,13 +6830,13 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -6847,24 +6887,25 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -6894,7 +6935,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -6906,7 +6947,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6924,28 +6965,28 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">770
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -6954,7 +6995,8 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>854</t>
+          <t xml:space="preserve">1252
+</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6965,8 +7007,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -7082,19 +7123,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">0527
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
+          <t xml:space="preserve">8021
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">11278
 </t>
         </is>
       </c>
@@ -7112,13 +7153,13 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -7130,16 +7171,19 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1050816
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1038
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1029
+</t>
+        </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
@@ -7151,24 +7195,25 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 9
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463
+          <t xml:space="preserve">1463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1384
 </t>
         </is>
       </c>
@@ -7180,37 +7225,37 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66 8
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">12340
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">2190
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99295
+          <t xml:space="preserve">3923
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
@@ -7255,13 +7300,13 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -7279,7 +7324,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -7291,7 +7336,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -7315,13 +7360,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -7357,7 +7402,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">2276
 </t>
         </is>
       </c>
@@ -7369,7 +7414,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -679,146 +679,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
-</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -838,146 +814,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -997,146 +949,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
-</t>
+          <t>596</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1156,146 +1084,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1315,146 +1219,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1474,146 +1354,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
-</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
-</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
-</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1345
-</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
-</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
-</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 82
-</t>
+          <t>12 82</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4870
-</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556
-</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
-</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
-</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
-</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1633,146 +1489,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
-</t>
+          <t>616</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1792,8 +1624,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1803,134 +1634,112 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
-</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1950,146 +1759,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2109,146 +1894,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
-</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2268,146 +2029,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
-</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2427,146 +2164,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23408
-</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2419
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>766</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2586,146 +2299,122 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15308
-</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
-</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2268
-</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
-</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
-</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">763
-</t>
+          <t>763</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
-</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
-</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423
-</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2745,146 +2434,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306
-</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2904,146 +2569,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3063,146 +2704,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3222,146 +2839,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3381,146 +2974,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18441
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3540,146 +3109,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
-</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12380
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3699,146 +3244,122 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
-</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
-</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
-</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
-</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>796</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
-</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3858,146 +3379,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4017,56 +3514,47 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
-</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4076,86 +3564,72 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4175,146 +3649,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
-</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4334,146 +3784,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4493,146 +3919,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2824
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4657,140 +4059,117 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4810,146 +4189,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
-</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11718
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
-</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
-</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
-</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4969,146 +4324,122 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
-</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
-</t>
+          <t>823</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5128,14 +4459,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
-</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5145,128 +4474,107 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5286,140 +4594,117 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Z33" s="3" t="n">
@@ -5442,44 +4727,37 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5489,98 +4767,82 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5600,146 +4862,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
-</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5759,146 +4997,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5918,146 +5132,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
-</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
-</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
-</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
-</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
-</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6077,146 +5267,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6236,146 +5402,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3323
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 8
-</t>
+          <t>0 08</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
-</t>
+          <t>729</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6395,146 +5537,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12006
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
-</t>
+          <t>654</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6554,44 +5672,37 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
@@ -6599,98 +5710,82 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6710,146 +5805,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6869,140 +5940,117 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -7027,8 +6075,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -7117,146 +6164,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14234
-</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0527
-</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11278
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
-</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
-</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12340
-</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7276,146 +6299,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
-</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>785</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>422</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>219</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>0 08</t>
+          <t>01 01</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_pre_QA_QC.xlsx
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>01 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>002</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>138</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
